--- a/data/trans_orig/P1805_2016_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1805_2016_2023-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>18090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23313</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15916</t>
+          <t>16639</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36098</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411934</t>
+          <t>411002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424330</t>
+          <t>424140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>323742</t>
+          <t>322923</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338534</t>
+          <t>337612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740049</t>
+          <t>740599</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>760231</t>
+          <t>759508</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25414</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>362853</t>
+          <t>362041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374292</t>
+          <t>374203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354916</t>
+          <t>355952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368835</t>
+          <t>368787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>724086</t>
+          <t>723937</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>740818</t>
+          <t>740744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35313</t>
+          <t>34915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>501047</t>
+          <t>499639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515206</t>
+          <t>514884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145545</t>
+          <t>145842</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160721</t>
+          <t>160639</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652723</t>
+          <t>653121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>672851</t>
+          <t>672966</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24301</t>
+          <t>24147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47218</t>
+          <t>49171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>35543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63268</t>
+          <t>63351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1125337</t>
+          <t>1125491</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1141897</t>
+          <t>1142154</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>778658</t>
+          <t>776705</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>802141</t>
+          <t>801974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1912246</t>
+          <t>1912163</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1940667</t>
+          <t>1939971</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>19152</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18207</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40560</t>
+          <t>41485</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27523</t>
+          <t>26459</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53423</t>
+          <t>53135</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>601813</t>
+          <t>601554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>615737</t>
+          <t>615537</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>697684</t>
+          <t>696759</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720037</t>
+          <t>719364</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1305527</t>
+          <t>1305815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1331427</t>
+          <t>1332491</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13919</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23072</t>
+          <t>22811</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46303</t>
+          <t>47143</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28670</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53401</t>
+          <t>55522</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>273226</t>
+          <t>274442</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284264</t>
+          <t>284288</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1035722</t>
+          <t>1034882</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1058953</t>
+          <t>1059214</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1315769</t>
+          <t>1313648</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1340500</t>
+          <t>1340178</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46664</t>
+          <t>46153</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>78788</t>
+          <t>78317</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>109008</t>
+          <t>106420</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158748</t>
+          <t>155675</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>164809</t>
+          <t>165408</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>223213</t>
+          <t>221190</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3306934</t>
+          <t>3307405</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3339058</t>
+          <t>3339569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3372848</t>
+          <t>3375921</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3422588</t>
+          <t>3425176</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6694105</t>
+          <t>6696128</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6752509</t>
+          <t>6751910</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -3361,32 +3361,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13767</t>
+          <t>12385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38907</t>
+          <t>36206</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3396,32 +3396,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>26636</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33880</t>
+          <t>36802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3431,32 +3431,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46407</t>
+          <t>48601</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33664</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>66038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3474,32 +3474,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>482920</t>
+          <t>528653</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>466305</t>
+          <t>514412</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491445</t>
+          <t>538233</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3509,32 +3509,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>423353</t>
+          <t>461775</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>413587</t>
+          <t>451609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430973</t>
+          <t>469725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3544,32 +3544,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>906272</t>
+          <t>990428</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>889742</t>
+          <t>972991</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>919015</t>
+          <t>1002529</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16179</t>
+          <t>16722</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10151</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25635</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>25219</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15597</t>
+          <t>17881</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32170</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3774,32 +3774,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>39417</t>
+          <t>41942</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>30551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51174</t>
+          <t>54382</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3817,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>436034</t>
+          <t>466490</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>426578</t>
+          <t>456431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>442062</t>
+          <t>473645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3852,32 +3852,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>359342</t>
+          <t>397924</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350410</t>
+          <t>387825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366983</t>
+          <t>405262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3887,32 +3887,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>795376</t>
+          <t>864413</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>783619</t>
+          <t>851973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>805670</t>
+          <t>875804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4047,32 +4047,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27990</t>
+          <t>23192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3767</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11961</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4117,32 +4117,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>13416</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34175</t>
+          <t>30952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -4160,32 +4160,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>654941</t>
+          <t>458096</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640274</t>
+          <t>448420</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664693</t>
+          <t>464960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4195,32 +4195,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159922</t>
+          <t>180148</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154950</t>
+          <t>174309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163144</t>
+          <t>183507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4230,32 +4230,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>814863</t>
+          <t>638244</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>801000</t>
+          <t>628157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827328</t>
+          <t>645693</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4390,32 +4390,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>35390</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20738</t>
+          <t>23294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45721</t>
+          <t>49326</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4425,32 +4425,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32984</t>
+          <t>37623</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14869</t>
+          <t>29125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46509</t>
+          <t>48781</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>64494</t>
+          <t>73013</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44498</t>
+          <t>55823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83475</t>
+          <t>90305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4503,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1003310</t>
+          <t>1096453</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>989098</t>
+          <t>1082517</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1014081</t>
+          <t>1108549</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4538,32 +4538,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>944544</t>
+          <t>822992</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>931019</t>
+          <t>811834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>962659</t>
+          <t>831490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4573,32 +4573,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1947853</t>
+          <t>1919445</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1928872</t>
+          <t>1902153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967849</t>
+          <t>1936635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4733,32 +4733,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5036</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4768,32 +4768,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>26105</t>
+          <t>26979</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17939</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37281</t>
+          <t>36704</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4803,32 +4803,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>36571</t>
+          <t>37984</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>27862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49190</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -4846,32 +4846,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>464579</t>
+          <t>556959</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>455248</t>
+          <t>547486</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>469527</t>
+          <t>562928</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4881,32 +4881,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>815230</t>
+          <t>803871</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>804054</t>
+          <t>794146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>823396</t>
+          <t>811281</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4916,32 +4916,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1279810</t>
+          <t>1360830</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1267191</t>
+          <t>1346974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1290274</t>
+          <t>1370952</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -4959,17 +4959,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5029,17 +5029,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29535</t>
+          <t>30565</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5111,32 +5111,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24282</t>
+          <t>26062</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>16431</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39334</t>
+          <t>39437</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5146,17 +5146,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>40206</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24761</t>
+          <t>25743</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55321</t>
+          <t>59922</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -5189,32 +5189,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>227530</t>
+          <t>223084</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210972</t>
+          <t>206663</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235143</t>
+          <t>231904</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5224,32 +5224,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>736410</t>
+          <t>817534</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>721358</t>
+          <t>804159</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>745504</t>
+          <t>827165</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5259,17 +5259,17 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>963941</t>
+          <t>1040618</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>945879</t>
+          <t>1020902</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>976439</t>
+          <t>1055081</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5302,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>106747</t>
+          <t>112742</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78454</t>
+          <t>88465</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133443</t>
+          <t>139871</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5454,32 +5454,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>137713</t>
+          <t>149869</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113616</t>
+          <t>129794</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>163538</t>
+          <t>175096</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5489,32 +5489,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>244460</t>
+          <t>262611</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>205046</t>
+          <t>234051</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>281502</t>
+          <t>298543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -5532,32 +5532,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3269313</t>
+          <t>3329734</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3242617</t>
+          <t>3302605</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3297606</t>
+          <t>3354011</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5567,32 +5567,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3438801</t>
+          <t>3484243</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3412976</t>
+          <t>3459016</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3462898</t>
+          <t>3504318</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5602,32 +5602,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6708114</t>
+          <t>6813977</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6671072</t>
+          <t>6778045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6747528</t>
+          <t>6842537</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -5645,17 +5645,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3576514</t>
+          <t>3634112</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3576514</t>
+          <t>3634112</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3576514</t>
+          <t>3634112</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5715,17 +5715,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6952574</t>
+          <t>7076588</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6952574</t>
+          <t>7076588</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6952574</t>
+          <t>7076588</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
